--- a/artfynd/A 33994-2023 artfynd.xlsx
+++ b/artfynd/A 33994-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33994-2023 artfynd.xlsx
+++ b/artfynd/A 33994-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>258839</v>
       </c>
       <c r="B2" t="n">
-        <v>89952</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>745211.2469829186</v>
+        <v>745211</v>
       </c>
       <c r="R2" t="n">
-        <v>7382938.11382267</v>
+        <v>7382938</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2012-10-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-10-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1897288</v>
+        <v>1897287</v>
       </c>
       <c r="B3" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745490.5573230522</v>
+        <v>745619</v>
       </c>
       <c r="R3" t="n">
-        <v>7382830.682305252</v>
+        <v>7382836</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,21 +845,11 @@
           <t>2012-08-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-08-14</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -891,7 +861,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Fin asprik bränna. Tätare, graninslag och aspkloner, nästan alla med skinnlav.</t>
+          <t>aspinslag. Spridda tallar något äldre men inga äldre än runt 200.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1998007</v>
+        <v>1897288</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745211.2469829186</v>
+        <v>745491</v>
       </c>
       <c r="R4" t="n">
-        <v>7382938.11382267</v>
+        <v>7382831</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,22 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2012-10-02</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2012-10-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,7 +963,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>liten fläck med gammelsälg, massor med lunglav och doftticka.</t>
+          <t>Fin asprik bränna. Tätare, graninslag och aspkloner, nästan alla med skinnlav.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1019,44 +974,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Robert Sandberg, Frédéric Forsmark</t>
+          <t>Via Sture Westerberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1897287</v>
+        <v>1998006</v>
       </c>
       <c r="B5" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>745618.7239728447</v>
+        <v>745116</v>
       </c>
       <c r="R5" t="n">
-        <v>7382836.408957154</v>
+        <v>7383047</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,22 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2012-08-14</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-10-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2012-08-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-10-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,7 +1065,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>aspinslag. Spridda tallar något äldre men inga äldre än runt 200.</t>
+          <t>hårt hugget men rikligt m gammal sälg.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1136,10 +1076,112 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Sture Westerberg</t>
+          <t>Robert Sandberg, Frédéric Forsmark</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1998007</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Padjerimberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>745211</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7382938</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2012-10-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2012-10-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>liten fläck med gammelsälg, massor med lunglav och doftticka.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Robert Sandberg, Frédéric Forsmark</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33994-2023 artfynd.xlsx
+++ b/artfynd/A 33994-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/258839</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1897287</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1897288</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1998006</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,8 +1207,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1998007</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>